--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_VNSH03_250626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_VNSH03_250626.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0365A7-9222-4804-A80B-E4167C7D3138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A027CE-F7BD-4561-8FA0-BFA79D30929C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId2"/>
+    <sheet name="ID" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">NhapKho_SX!$A$1:$M$20</definedName>
